--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -413,736 +413,1215 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Measured by operator 7 on tool HRM-2</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Outer Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17.05181</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.31073</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.31922</v>
+      </c>
+      <c r="F2" t="n">
+        <v>54.67138</v>
+      </c>
+      <c r="G2" t="n">
+        <v>42.74878</v>
+      </c>
+      <c r="H2" t="n">
+        <v>85.97441000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.04973</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.76195</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.63028</v>
+        <v>16.95866</v>
       </c>
       <c r="D3" t="n">
-        <v>16.38473</v>
+        <v>16.46154</v>
       </c>
       <c r="E3" t="n">
-        <v>16.2993</v>
+        <v>16.87328</v>
       </c>
       <c r="F3" t="n">
-        <v>42.2757</v>
+        <v>54.97578</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05043</v>
+        <v>42.99275</v>
       </c>
       <c r="H3" t="n">
-        <v>1.831</v>
+        <v>84.07451</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.04986</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.81719</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.69592</v>
+        <v>17.05896</v>
       </c>
       <c r="D4" t="n">
-        <v>16.1934</v>
+        <v>16.41672</v>
       </c>
       <c r="E4" t="n">
-        <v>16.57451</v>
+        <v>16.53004</v>
       </c>
       <c r="F4" t="n">
-        <v>41.68405</v>
+        <v>55.20403</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05008</v>
+        <v>41.39059</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83247</v>
+        <v>84.18789</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.80528</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.82637</v>
+        <v>16.67073</v>
       </c>
       <c r="D5" t="n">
-        <v>16.42333</v>
+        <v>16.42705</v>
       </c>
       <c r="E5" t="n">
-        <v>16.58834</v>
+        <v>16.62</v>
       </c>
       <c r="F5" t="n">
-        <v>42.79297</v>
+        <v>55.38369</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05079</v>
+        <v>42.02112</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83501</v>
+        <v>85.45735000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.81778</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.42528</v>
+        <v>16.78838</v>
       </c>
       <c r="D6" t="n">
-        <v>16.31813</v>
+        <v>16.56076</v>
       </c>
       <c r="E6" t="n">
-        <v>16.64732</v>
+        <v>16.67064</v>
       </c>
       <c r="F6" t="n">
-        <v>42.14718</v>
+        <v>56.78723</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04974</v>
+        <v>42.42342</v>
       </c>
       <c r="H6" t="n">
-        <v>1.85294</v>
+        <v>85.90474</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.04953</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.76982</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.92177</v>
+        <v>16.86844</v>
       </c>
       <c r="D7" t="n">
-        <v>16.3261</v>
+        <v>16.24241</v>
       </c>
       <c r="E7" t="n">
-        <v>16.48136</v>
+        <v>16.5815</v>
       </c>
       <c r="F7" t="n">
-        <v>41.87713</v>
+        <v>55.37937</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04989</v>
+        <v>42.11743</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81289</v>
+        <v>86.36399</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.82136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.7054</v>
+        <v>17.21557</v>
       </c>
       <c r="D8" t="n">
-        <v>16.31542</v>
+        <v>16.53632</v>
       </c>
       <c r="E8" t="n">
-        <v>16.55523</v>
+        <v>16.67426</v>
       </c>
       <c r="F8" t="n">
-        <v>42.62844</v>
+        <v>55.33878</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05074</v>
+        <v>42.56043</v>
       </c>
       <c r="H8" t="n">
-        <v>1.78958</v>
+        <v>84.82597</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05048</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.8371</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.43944</v>
+        <v>16.5903</v>
       </c>
       <c r="D9" t="n">
-        <v>16.08262</v>
+        <v>16.43084</v>
       </c>
       <c r="E9" t="n">
-        <v>16.66964</v>
+        <v>16.50908</v>
       </c>
       <c r="F9" t="n">
-        <v>42.85811</v>
+        <v>55.4936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05044</v>
+        <v>42.39843</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79886</v>
+        <v>83.69566</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.04951</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.81941</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.9806</v>
+        <v>16.95399</v>
       </c>
       <c r="D10" t="n">
-        <v>16.39601</v>
+        <v>16.36419</v>
       </c>
       <c r="E10" t="n">
-        <v>16.76788</v>
+        <v>16.76273</v>
       </c>
       <c r="F10" t="n">
-        <v>42.46356</v>
+        <v>55.53173</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05018</v>
+        <v>42.23065</v>
       </c>
       <c r="H10" t="n">
-        <v>1.78636</v>
+        <v>86.14885</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.82911</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.87581</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.26479</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.76104</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41.52857</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05058</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.79362</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Outer Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16.65902</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.64356</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.65378</v>
+      </c>
+      <c r="F12" t="n">
+        <v>56.6103</v>
+      </c>
+      <c r="G12" t="n">
+        <v>42.09515</v>
+      </c>
+      <c r="H12" t="n">
+        <v>84.24097</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0501</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.80815</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5990799999999999</v>
+        <v>17.28023</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1042</v>
+        <v>16.36123</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.60342</v>
+      </c>
+      <c r="F13" t="n">
+        <v>55.85581</v>
+      </c>
+      <c r="G13" t="n">
+        <v>42.92752</v>
+      </c>
+      <c r="H13" t="n">
+        <v>83.27728999999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05022</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.82585</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.60706</v>
+        <v>16.74879</v>
       </c>
       <c r="D14" t="n">
-        <v>1.09389</v>
+        <v>16.54644</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.66844</v>
+      </c>
+      <c r="F14" t="n">
+        <v>54.69331</v>
+      </c>
+      <c r="G14" t="n">
+        <v>42.57362</v>
+      </c>
+      <c r="H14" t="n">
+        <v>85.38943</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.8073</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.59036</v>
+        <v>16.4939</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1036</v>
+        <v>16.40041</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.46935</v>
+      </c>
+      <c r="F15" t="n">
+        <v>55.60643</v>
+      </c>
+      <c r="G15" t="n">
+        <v>41.33987</v>
+      </c>
+      <c r="H15" t="n">
+        <v>82.99713</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05076</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.78438</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5986900000000001</v>
+        <v>16.88336</v>
       </c>
       <c r="D16" t="n">
-        <v>1.12412</v>
+        <v>16.36997</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.43921</v>
+      </c>
+      <c r="F16" t="n">
+        <v>54.76687</v>
+      </c>
+      <c r="G16" t="n">
+        <v>41.88203</v>
+      </c>
+      <c r="H16" t="n">
+        <v>83.95368000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.05104</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.82953</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.59795</v>
+        <v>16.68066</v>
       </c>
       <c r="D17" t="n">
-        <v>1.11644</v>
+        <v>16.19141</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.5401</v>
+      </c>
+      <c r="F17" t="n">
+        <v>56.11676</v>
+      </c>
+      <c r="G17" t="n">
+        <v>42.04812</v>
+      </c>
+      <c r="H17" t="n">
+        <v>84.90808</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05085</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.80564</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.59948</v>
+        <v>16.52061</v>
       </c>
       <c r="D18" t="n">
-        <v>1.10335</v>
+        <v>16.23625</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.4078</v>
+      </c>
+      <c r="F18" t="n">
+        <v>55.30514</v>
+      </c>
+      <c r="G18" t="n">
+        <v>42.57228</v>
+      </c>
+      <c r="H18" t="n">
+        <v>84.69748</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05128</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.84575</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60304</v>
+        <v>16.88261</v>
       </c>
       <c r="D19" t="n">
-        <v>1.13708</v>
+        <v>16.34163</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.4158</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.11118</v>
+      </c>
+      <c r="G19" t="n">
+        <v>42.50211</v>
+      </c>
+      <c r="H19" t="n">
+        <v>85.32155</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.04984</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.79096</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.60952</v>
+        <v>16.89325</v>
       </c>
       <c r="D20" t="n">
-        <v>1.11455</v>
+        <v>16.63996</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.79586</v>
+      </c>
+      <c r="F20" t="n">
+        <v>54.30002</v>
+      </c>
+      <c r="G20" t="n">
+        <v>42.46675</v>
+      </c>
+      <c r="H20" t="n">
+        <v>83.48189000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.05124</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.8264</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.59776</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.11557</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>16.73291</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.74992</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.29276</v>
+      </c>
+      <c r="F22" t="n">
+        <v>21.64775</v>
+      </c>
+      <c r="G22" t="n">
+        <v>33.56128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.73698</v>
+        <v>16.57554</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08187</v>
+        <v>15.71864</v>
       </c>
       <c r="E23" t="n">
-        <v>0.60267</v>
+        <v>16.14197</v>
       </c>
       <c r="F23" t="n">
-        <v>0.95109</v>
+        <v>21.55161</v>
       </c>
       <c r="G23" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09268999999999999</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.1248</v>
+        <v>33.86142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.74286</v>
+        <v>16.50795</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08066</v>
+        <v>15.86535</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6029</v>
+        <v>16.3734</v>
       </c>
       <c r="F24" t="n">
-        <v>0.94129</v>
+        <v>21.72995</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1083</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00739</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.0929</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12598</v>
+        <v>34.1501</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7380100000000001</v>
+        <v>16.7655</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07981000000000001</v>
+        <v>16.01696</v>
       </c>
       <c r="E25" t="n">
-        <v>0.60862</v>
+        <v>16.2851</v>
       </c>
       <c r="F25" t="n">
-        <v>0.95617</v>
+        <v>21.61082</v>
       </c>
       <c r="G25" t="n">
-        <v>0.11016</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00761</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09386</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12267</v>
+        <v>34.58146</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.74537</v>
+        <v>16.54225</v>
       </c>
       <c r="D26" t="n">
-        <v>0.07972</v>
+        <v>15.83745</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60407</v>
+        <v>16.2908</v>
       </c>
       <c r="F26" t="n">
-        <v>0.92658</v>
+        <v>21.27707</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1074</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00783</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09168999999999999</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12594</v>
+        <v>34.76184</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.74251</v>
+        <v>16.62189</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08123</v>
+        <v>16.01462</v>
       </c>
       <c r="E27" t="n">
-        <v>0.59718</v>
+        <v>16.50252</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9436600000000001</v>
+        <v>21.21921</v>
       </c>
       <c r="G27" t="n">
-        <v>0.10726</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09002</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12597</v>
+        <v>33.99557</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.73212</v>
+        <v>16.41901</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08026</v>
+        <v>16.1495</v>
       </c>
       <c r="E28" t="n">
-        <v>0.60872</v>
+        <v>16.3889</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9750799999999999</v>
+        <v>21.51371</v>
       </c>
       <c r="G28" t="n">
-        <v>0.10859</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00743</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09082</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12831</v>
+        <v>34.27073</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.74085</v>
+        <v>16.63967</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08001</v>
+        <v>16.13997</v>
       </c>
       <c r="E29" t="n">
-        <v>0.58957</v>
+        <v>16.48482</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9654700000000001</v>
+        <v>21.46293</v>
       </c>
       <c r="G29" t="n">
-        <v>0.11002</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09224</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12554</v>
+        <v>34.22935</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.48906</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.76663</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.40696</v>
+      </c>
+      <c r="F30" t="n">
+        <v>20.97292</v>
+      </c>
+      <c r="G30" t="n">
+        <v>33.90019</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.07907</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.60963</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.95533</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.10651</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09293999999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12428</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.74682</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08185000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6111</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.9769099999999999</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.10786</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09200999999999999</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12665</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.74226</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08048</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.60193</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.94693</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.10886</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09432</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12505</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.74103</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08214</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.60999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.96975</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.10672</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12672</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.75367</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08086</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.60349</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.96892</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.10762</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09189</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12646</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.73209</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.07965999999999999</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.61172</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.99677</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.10806</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00747</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09202</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12653</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.75296</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08022</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6035700000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.10704</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09347999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12924</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.74002</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.07832</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.59998</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.9331</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.11065</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09207</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.1269</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="C39" t="n">
+        <v>0.74929</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.07979</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.59496</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.95803</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10815</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09191000000000001</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12629</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>0.75034</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.07911</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.60639</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.9465</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.10914</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I31" t="n">
+      <c r="C40" t="n">
+        <v>0.75786</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.07871</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.60572</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9684</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.11066</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.09314</v>
       </c>
-      <c r="J31" t="n">
-        <v>0.12711</v>
+      <c r="J40" t="n">
+        <v>0.12415</v>
       </c>
     </row>
   </sheetData>
